--- a/eoptolink/dist/20261028_新易盛個股模型_v0.2.3.xlsx
+++ b/eoptolink/dist/20261028_新易盛個股模型_v0.2.3.xlsx
@@ -6397,26 +6397,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中際旭創模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">innolight/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中際旭創個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6704,26 +6704,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中際旭創模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">innolight/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中際旭創個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/eoptolink/dist/20261028_新易盛個股模型_v0.2.3.xlsx
+++ b/eoptolink/dist/20261028_新易盛個股模型_v0.2.3.xlsx
@@ -6105,7 +6105,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261028_</t>
+      <t xml:space="preserve">innolight/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6124,7 +6124,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.3.xlsx</t>
+      <t xml:space="preserve">_v0.2.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6412,7 +6412,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261028_</t>
+      <t xml:space="preserve">innolight/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6431,7 +6431,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.3.xlsx</t>
+      <t xml:space="preserve">_v0.2.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6579,7 +6579,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6598,7 +6598,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6816,7 +6816,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6835,7 +6835,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6937,7 +6937,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6956,7 +6956,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7058,7 +7058,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7077,7 +7077,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7179,7 +7179,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7198,7 +7198,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7300,7 +7300,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7319,7 +7319,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
